--- a/site/Paycor-to-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Paycor-to-Entra-ID-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/site/Paycor-to-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Paycor-to-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Entra-ID-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
